--- a/ABA_mining/outputs/eval/task3/price/llama3.2/contrary_v6/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/price/llama3.2/contrary_v6/EVAL_SUMMARY.xlsx
@@ -541,16 +541,16 @@
         <v>97</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8964497041420119</v>
+        <v>0.89645</v>
       </c>
       <c r="M2" t="n">
         <v>0.7575</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8211382113821138</v>
+        <v>0.821138</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7098901098901099</v>
+        <v>0.70989</v>
       </c>
     </row>
     <row r="3">
@@ -600,16 +600,16 @@
         <v>98</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8961424332344213</v>
+        <v>0.896142</v>
       </c>
       <c r="M3" t="n">
         <v>0.755</v>
       </c>
       <c r="N3" t="n">
-        <v>0.819538670284939</v>
+        <v>0.819538</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7076923076923077</v>
+        <v>0.707692</v>
       </c>
     </row>
     <row r="4">
@@ -659,16 +659,16 @@
         <v>97</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8964497041420119</v>
+        <v>0.89645</v>
       </c>
       <c r="M4" t="n">
         <v>0.7575</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8211382113821138</v>
+        <v>0.821138</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7098901098901099</v>
+        <v>0.70989</v>
       </c>
     </row>
   </sheetData>
@@ -784,16 +784,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.8963474827245804</v>
+        <v>0.896347</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7566666666666667</v>
+        <v>0.756667</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8206055128784456</v>
+        <v>0.8206059999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7091575091575092</v>
+        <v>0.709158</v>
       </c>
       <c r="J2" t="n">
         <v>1365</v>
